--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44865</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>46076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45635</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45975</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45825</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45929</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>45974</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45975</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>46077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44790</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>44915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45929</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45726</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>46179</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44855</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>45972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45975</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45611</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45807</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44552</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45946</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>45954</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45961</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45994</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45590</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>45576</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>46178</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>46190</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>45617</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>46099</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45105</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>46247</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>46253</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>46212</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>46272</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>46273</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45981</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>46241</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>45105</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45800</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44690</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>44715</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>44845</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44511</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44621</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44543</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44489</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44624</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44883</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44735</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44792</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44483</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44543</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44741</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44511</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45442</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>45329</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45090</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45589</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44804</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45001</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45617</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45099</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45309</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45201</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45545</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45478</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44979</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45303</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45475</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45364</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45470</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44700</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>45149</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45225</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>44825</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45593</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45612</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>44911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45502</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>44942</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>44944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45462</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>45889</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45890</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>45590</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>44497</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45594</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45933</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45450</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>45616</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45911</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45910</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45950</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45726</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45191</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45917</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45919</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45919</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45922</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45922</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45923</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45924</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45924</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45084</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45538</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45225</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45929</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45786</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45933</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45933</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45932</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>46146</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>46147</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>46146</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46146</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>46146</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45937</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>46146</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45939</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45448</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45448</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44860</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45944</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45946</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46148</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45950</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45310</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45957</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45954</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45590</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45964</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45965</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45965</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45972</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45972</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45975</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45975</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45975</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45975</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45975</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45974</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45978</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45978</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45726</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45726</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45982</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45984</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45726</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45986</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45986</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45595</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45818</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45723</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45995</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45996</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>46164</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>46169</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>44819</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45590</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>45558</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45919</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>46010</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45960</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45993</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45981</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45560</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>46029</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>46170</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45617</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>45484</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45484</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>46034</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45476</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>46034</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46035</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>46173</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>46173</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>46034</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45726</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45538</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45636</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46045</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46045</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>46050</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>46052</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>46052</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45590</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44988</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>46179</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>46056</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45166</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45470</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46178</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>46179</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46034</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46182</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>46181</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>46182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45517</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>46072</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>46182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>46076</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>46076</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45595</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>46083</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46084</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>46084</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46182</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46084</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45152</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45152</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>46188</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45450</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>46188</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45454</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>46188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45225</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45093</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45551</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45470</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45461</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46197</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>46104</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45593</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45628</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>46199</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>46199</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45467</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>46126</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>46202</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45365</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>46245</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46202</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44977</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45625</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45020</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45579</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45103</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44861</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45616</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46247</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45364</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45722</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>46206</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>46206</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>46206</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45702</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45726</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>46205</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>46205</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45646</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46206</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46245</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45448</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45244</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45176</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>46252</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44463</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>46211</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46212</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46212</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>46252</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45590</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>46252</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45722</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45103</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>46259</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>46259</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46261</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>45316</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45222</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>46262</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>46262</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>46262</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45361</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>46265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>44915</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46265</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>46253</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46266</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46253</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45726</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>46266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>46266</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>46261</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46266</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>46268</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45470</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45470</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45315</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46268</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>46273</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>46268</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>46268</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46231</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45173</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>46281</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45166</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45726</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45726</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45454</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>44804</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>46281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46240</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46239</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46241</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46241</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45798</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45677</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>46280</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>44732</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45805</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44699</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44804</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45805</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45590</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45805</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45805</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45805</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>44865</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44497</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45329</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45818</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45820</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45825</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45827</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45840</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45841</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45859</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>44855</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45869</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45875</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45875</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45877</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45881</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45881</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45881</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45394</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45404</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45448</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45412</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45433</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45012</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45219</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45404</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>45408</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45447</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45412</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45785</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45799</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45799</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45799</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>45919</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46146</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46146</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>46148</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46149</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>46148</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46167</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46168</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>46168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>46211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>46076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46077</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45975</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45929</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46179</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45807</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45975</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45611</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45105</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45576</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45946</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45954</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45961</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45994</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45995</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45617</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46178</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>46253</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>46212</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>46272</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>46273</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>46241</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44690</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44715</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44690</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44487</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44489</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44624</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44543</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45450</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45545</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45502</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45992</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45993</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45960</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45960</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45881</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45310</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45226</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44942</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44497</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45798</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45579</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45476</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45888</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45677</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>46035</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45484</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45726</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44911</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45538</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44915</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>46045</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45475</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45517</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>46045</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45674</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>46050</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>46052</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45910</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>46052</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>46056</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46056</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45911</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45922</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45919</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45919</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45922</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45924</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45923</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45364</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>46076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>46072</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>46076</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>46083</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45805</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45805</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45805</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44804</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>46084</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>46084</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45933</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45560</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45933</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45937</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45937</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45939</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45825</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45448</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45142</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>44497</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45944</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45950</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>46104</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45103</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45954</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45957</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45964</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45965</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45965</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45965</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>46126</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45972</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44865</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45972</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45329</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45975</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45978</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45975</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45978</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45975</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45818</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45975</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45612</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45590</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45595</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45982</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45984</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45986</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45985</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45988</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45470</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45722</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45726</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45723</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45646</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45996</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45995</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45726</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45726</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45225</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45636</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45625</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45919</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45820</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45538</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>46010</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>45769</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45616</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45244</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45825</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45825</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45786</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45827</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46146</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46146</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45726</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>46146</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46146</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46147</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45467</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44904</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44915</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45818</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45840</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>46164</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45841</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45364</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45365</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45448</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>46169</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46173</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46173</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45859</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44855</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>46170</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>46170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45166</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45152</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44977</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45869</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46182</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45149</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>46178</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>46181</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>46179</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>46179</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45590</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46182</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45617</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44979</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45558</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45167</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45329</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45442</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46188</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46188</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45103</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45875</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46006</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45470</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45877</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46197</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45702</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45881</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45617</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45881</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>46202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45726</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46202</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45722</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46205</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>46205</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46252</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45590</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>46252</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46206</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44804</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>46252</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>46252</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45594</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>46252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>46212</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>46259</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>46259</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44700</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46262</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>46261</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>46262</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46262</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45462</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>46266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46261</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46265</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>46265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>46266</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46253</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45316</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>46268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45309</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>46268</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>46268</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46268</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46268</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46268</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46273</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46231</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45484</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45590</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45448</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46280</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45225</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>46281</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>46239</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45537</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45191</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45589</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45616</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46240</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>46084</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45225</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>46286</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>46286</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>46286</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>46241</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46241</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46245</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>46288</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46245</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>46084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>46288</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45722</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45722</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45001</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45478</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46286</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45590</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45932</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>46247</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45590</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44861</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45593</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45093</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45470</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45470</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45152</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45103</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44988</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45454</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45593</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45201</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45303</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45728</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45602</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45628</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45361</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>44825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45176</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45470</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>45315</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45470</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45114</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45166</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45726</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45173</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45726</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44804</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45454</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45394</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45404</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45448</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45412</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45433</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45012</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45219</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45404</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45408</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45447</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45412</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45785</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45799</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45799</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45799</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45919</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>46146</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46146</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>46148</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46149</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>46168</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>46167</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>46076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46077</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45975</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45929</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46179</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45807</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45975</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45611</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45105</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45576</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45946</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45954</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45961</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45994</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45995</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45820</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45617</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46178</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>46253</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>46212</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>46272</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>46273</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>46241</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44690</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44715</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44690</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44487</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44489</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44624</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44543</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>44819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45450</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45545</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45502</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45992</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45993</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45960</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45960</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45881</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45310</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45226</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44942</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44497</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45798</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45579</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45476</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45888</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45677</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>46035</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45484</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45726</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44911</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45538</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44915</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>46045</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45475</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45517</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>46045</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45674</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>46050</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>46052</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45910</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>46052</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>46056</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46056</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45911</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45922</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45919</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45919</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45922</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45924</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45923</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45364</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>46076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>46072</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>46076</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>46083</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45805</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45805</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45805</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44804</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>46084</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>46084</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45933</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45560</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45933</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45937</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45937</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45939</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45825</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45448</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45142</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>44497</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45944</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45950</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>46104</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45103</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45954</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45957</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45964</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45965</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45965</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>45965</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>46126</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45972</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44865</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45972</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45329</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45975</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45978</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45975</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45978</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45975</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45818</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45975</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45612</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45590</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45595</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45982</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45984</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45986</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45985</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45988</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45470</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45722</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45726</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45723</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45646</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45996</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45995</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45726</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45726</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45225</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45636</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45625</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45919</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45820</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45538</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>46010</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>45769</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45616</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45244</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45825</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45825</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45786</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45827</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46146</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46146</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45726</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>46146</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46146</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46147</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45467</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44904</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44915</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45818</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45840</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>46164</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45841</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45364</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45365</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45448</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>46169</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46173</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46173</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45859</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44855</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>46170</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>46170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45166</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45152</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44977</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45869</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46182</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45149</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>46178</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>46181</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>46179</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>46179</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45590</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46182</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45617</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44979</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45558</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45167</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45329</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45442</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46188</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46188</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45103</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45875</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46006</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45470</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45877</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46197</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45702</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45881</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45617</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45881</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>46202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45726</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46202</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45722</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46205</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>46205</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46252</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45590</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>46252</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46206</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44804</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>46252</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45090</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>46252</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45594</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>46252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>46212</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>46259</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>46259</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44700</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46262</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>46261</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>46262</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46262</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45462</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>46266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>46266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46261</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46265</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>46265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>46266</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46253</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45316</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>46268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45309</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>46268</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>46268</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46268</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46268</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46268</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46273</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46231</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45484</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45590</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45448</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46280</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45225</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>46281</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>46239</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45537</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45191</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45589</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45616</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46240</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>46084</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45225</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>46286</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>46286</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>46286</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>46241</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46241</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46245</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>46288</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46245</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>46084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>46288</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45722</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45722</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45001</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45478</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46286</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45590</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45932</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>46247</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45590</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44861</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45593</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45093</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45470</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45470</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45152</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45103</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44988</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45454</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45593</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45201</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45303</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45728</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45602</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45628</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45361</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>44825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45176</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45470</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>45315</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45470</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45114</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45166</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45726</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45173</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45726</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44804</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45454</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45394</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45404</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45448</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45412</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45433</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45012</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45219</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45404</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45408</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45447</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45412</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45785</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45799</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45799</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45799</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45919</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>46146</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46146</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>46148</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46149</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>46168</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>46167</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>46076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44865</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46077</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45975</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46179</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45807</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45975</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45726</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45611</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45105</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45946</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45954</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45961</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>46099</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45820</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45994</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45995</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>46178</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>46190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45590</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>46212</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45617</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46241</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>46247</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46253</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44690</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44715</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44690</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44487</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44489</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44624</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44543</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45090</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45442</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45142</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45329</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45617</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45589</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45173</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44497</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45166</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45726</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44911</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45454</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45478</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45309</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45769</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45992</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45981</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45889</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45888</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45890</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45974</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45201</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>46034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>46035</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>46034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45726</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>46045</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>46045</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44979</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45798</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45677</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>46050</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45919</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44732</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44699</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>44804</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45805</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45805</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45805</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45805</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45922</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>46052</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>46052</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45923</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45303</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45924</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46056</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46056</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45929</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45929</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45929</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45728</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45475</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45933</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45470</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45364</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45933</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>46034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45937</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46072</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45939</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45825</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45944</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45944</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45944</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>46076</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45602</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44700</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>46083</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>44865</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46084</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45957</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45149</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45954</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44497</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45954</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45225</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>44825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45329</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45964</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45965</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45972</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45972</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45974</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45975</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45975</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45975</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45974</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45818</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45820</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45982</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45502</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45593</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45985</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45986</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45612</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45986</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45825</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>44911</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45825</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>44942</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45827</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45723</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45950</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44944</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45996</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45462</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45226</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45594</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45840</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45841</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45450</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45191</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45084</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45859</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44855</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45225</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45616</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45869</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45950</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45448</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45448</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>44860</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45537</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45538</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45786</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45310</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>46147</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46146</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46146</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>46146</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46146</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>46148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45590</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45875</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45818</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>46164</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45877</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45726</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45726</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45726</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>46170</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>46170</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46173</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45881</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45881</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>46179</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>46178</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>46179</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>46183</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>46181</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>46182</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>46182</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46188</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>46188</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44819</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46197</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45558</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46006</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45560</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>46202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45484</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45484</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46206</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45476</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>46206</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>46205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>46206</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>46211</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45538</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45636</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46212</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>46212</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46259</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>46259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>46261</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45590</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45166</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>45470</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>46262</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>46262</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>46262</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>46265</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>46265</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>46266</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>46266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46266</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>46261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>46266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>45517</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>46268</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>46268</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>46268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>46273</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46268</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>46273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>46273</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>46231</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45152</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45152</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45450</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45454</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45225</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>46281</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>45470</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46240</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46239</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45461</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46280</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45722</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>46286</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>46286</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45722</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>46084</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>46241</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>46286</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45628</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>46286</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46241</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46288</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45467</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45590</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45365</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45932</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46247</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>46245</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44977</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>46252</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45625</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>46252</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45020</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45579</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46252</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45103</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>44861</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>46252</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46252</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45616</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45364</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46253</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45881</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45702</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46076</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45726</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46253</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45448</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45176</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45590</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45103</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45316</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45222</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45361</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>44915</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45726</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45470</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45470</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45315</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45114</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45394</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45404</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45404</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45448</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45448</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45412</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45433</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45012</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45219</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45408</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45447</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45448</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45013</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45412</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45785</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45799</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45799</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45799</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45799</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45919</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46146</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>46146</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46146</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>46146</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46146</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>46146</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46148</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46148</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>46148</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>46149</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>46148</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>46168</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>46168</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>46168</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>46175</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>46211</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>46076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44865</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44797</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46077</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45975</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46179</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45807</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45975</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45726</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45611</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45105</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45946</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45954</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45961</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>46099</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45820</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45994</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45995</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>46178</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>46190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45590</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>46212</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45617</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46241</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>46247</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46253</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44690</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44715</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44690</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44487</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44489</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44624</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44543</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45090</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45442</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45142</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45329</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45617</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45589</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44804</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45173</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44497</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45166</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45726</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44911</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45454</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45478</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45309</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45769</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45992</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45981</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45889</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45888</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45890</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45974</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45201</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>46034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>46035</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>46034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45726</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>46045</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>46045</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44979</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45798</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45677</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>46050</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45919</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44732</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44699</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>44804</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45805</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45805</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45805</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45805</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45922</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>46052</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>46052</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45923</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45303</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45924</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46056</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46056</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45929</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45929</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45929</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45728</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45475</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45933</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45470</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45364</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45933</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>46034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45937</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46072</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45939</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45825</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45944</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45944</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45944</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>46076</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45602</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44700</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>46083</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>44865</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46084</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45957</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45149</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45954</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44497</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45954</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45225</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>44825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45329</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45964</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45965</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45972</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45972</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45974</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45975</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45975</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45975</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45974</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45818</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45820</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45982</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45502</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45593</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45985</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45986</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45612</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45986</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45825</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>44911</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45825</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>44942</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45827</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45723</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45950</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44944</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45996</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45462</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45226</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45594</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45840</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45841</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45450</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45191</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45084</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45859</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44855</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45225</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45616</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45869</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45950</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45448</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45448</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>44860</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45537</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45538</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45786</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45310</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>46147</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46146</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46146</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>46146</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46146</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>46148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45590</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45875</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45818</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>46164</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45877</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45726</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45726</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45726</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>46170</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>46170</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46173</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45881</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45881</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>46179</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>46178</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>46179</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>46183</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>46181</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>46182</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>46182</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46188</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46188</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>46188</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44819</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46197</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45558</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46006</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45560</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>46202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45484</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45484</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46206</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45476</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>46206</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>46205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>46205</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>46206</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>46211</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45538</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45636</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46212</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>46212</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44915</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46259</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>46259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>46261</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45590</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45166</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>45470</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>46262</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>46262</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>46262</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>46265</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>46265</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>46266</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>46266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46266</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>46261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>46266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>45517</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>46268</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>46268</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>46268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>46273</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46268</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>46273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>46273</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>46231</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45152</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45152</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45450</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45454</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45225</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>46281</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>45470</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46240</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46239</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45461</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46280</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45722</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>46286</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>46286</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45722</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>46084</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>46241</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>46286</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45628</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>46286</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46241</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>46286</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46288</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45467</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45590</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45365</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45932</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46247</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>46245</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44977</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>46252</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45625</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>46252</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45020</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45579</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46252</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45103</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>44861</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>46252</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46252</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45616</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45364</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46253</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45881</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45702</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46076</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45726</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46253</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45448</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45176</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45590</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45103</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45316</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45222</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45361</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>44915</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45726</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45470</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45470</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45315</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45114</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45394</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45404</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45404</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45448</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45448</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45412</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45433</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45012</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45219</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45408</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45447</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45448</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45013</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45412</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45785</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45799</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45799</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45799</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45799</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45919</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46146</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>46146</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46146</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>46146</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46146</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>46146</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46148</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46148</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>46148</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>46149</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>46148</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>46168</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>46168</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>46168</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>46175</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>46211</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>45975</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45975</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46077</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45929</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>46179</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45807</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45611</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45975</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46034</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45576</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45105</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45590</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45946</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45954</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45961</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45617</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>46099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45994</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45105</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>46178</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>46212</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>46272</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>46273</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>45981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46241</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>46247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46253</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>46302</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45800</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44690</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44845</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44690</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44487</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44483</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44489</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>44543</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44812</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>44624</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44721</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44792</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44741</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44511</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44904</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44915</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45454</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45201</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45461</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45303</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45728</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45450</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45364</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44944</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45448</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45881</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45502</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45628</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44497</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45310</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45361</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45226</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44825</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45888</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44942</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45166</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45579</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45476</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45484</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45152</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44977</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44915</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45910</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45176</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>45149</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45910</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45475</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45517</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>45674</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45911</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45470</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45315</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45590</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45114</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45617</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44979</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45558</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45329</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45917</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45442</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45922</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45103</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45919</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45919</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45919</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45919</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45922</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45919</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45166</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45924</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45924</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45726</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45173</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45726</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45923</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45364</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45470</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44804</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45929</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45454</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44860</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45929</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45929</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45702</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45722</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45932</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45560</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45798</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45677</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45726</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45933</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44732</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45450</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45933</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45937</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45448</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45142</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45805</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45805</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44699</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45805</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44804</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45103</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45939</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44497</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45944</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45944</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44804</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45946</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>44865</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45329</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45950</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45818</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45820</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45825</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45825</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45827</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45954</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45954</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45957</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45020</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44700</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45964</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45612</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45965</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45840</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45841</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45462</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45972</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45974</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45470</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45726</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45972</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45646</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45975</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45726</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45859</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44855</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45726</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45316</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45309</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45225</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45636</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45625</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45975</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45975</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45869</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45875</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45877</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45881</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45982</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45099</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45590</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45244</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45986</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45984</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45986</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45448</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45537</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45191</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>45589</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45988</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45726</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45726</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45616</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45225</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45723</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45996</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45001</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>45478</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45919</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45590</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44861</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46010</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45981</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45993</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45993</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45960</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45593</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45093</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45974</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46029</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46034</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45470</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>46034</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>46034</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45950</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>46034</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>46035</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45538</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45470</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45726</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45152</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45103</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45616</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46045</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46045</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>46050</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44988</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46052</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45786</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46052</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>46056</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>46056</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>46146</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28490,7 +28490,7 @@
         <v>46146</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>46146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>46146</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>46146</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>46148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>46034</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>46147</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46076</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>46072</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>46083</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>46084</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>46084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>46164</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>46169</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46173</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>46173</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46170</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>46170</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>46178</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46181</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46179</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>46179</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>46182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>46183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>46182</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>46188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>46188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>46188</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>46188</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>46182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>46006</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46197</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>46202</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>46202</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45722</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46205</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46205</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46206</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46206</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>46206</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>46206</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>46211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>46212</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46212</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>46266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46265</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>46265</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46266</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>46266</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46268</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>46268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>46268</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>46268</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>46268</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>46268</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>46273</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>46231</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>46280</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>46239</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>46286</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>46240</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46084</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>46286</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46286</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46286</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>46286</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>46241</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>46241</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46245</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>46288</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46084</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46288</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45722</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45722</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>46286</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45932</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>46247</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>46252</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>46245</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46253</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46252</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46253</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46252</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46252</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46252</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45881</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46076</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>46259</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>46259</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>46262</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>46302</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>46261</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>46302</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>46262</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>46304</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>46304</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46261</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>46304</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>46262</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46304</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>45394</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45404</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45448</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45412</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45433</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45012</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45219</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45404</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45408</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45447</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45412</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45785</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45799</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45799</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45799</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45919</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>46146</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>46146</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46148</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46149</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46168</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46167</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>45975</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45975</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46077</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45929</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>46179</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45807</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45611</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45975</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46034</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45576</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45105</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45590</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45946</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45954</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45961</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45617</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>46099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45994</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45105</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>46178</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>46212</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>46272</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>46273</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>45981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46241</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>46247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46253</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>46302</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45800</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44690</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44845</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44690</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44487</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44483</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44489</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>44543</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44487</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44812</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>44624</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44721</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44792</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44741</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44819</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44511</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44904</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44915</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45454</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45201</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45461</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45303</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45728</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45450</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45364</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44944</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45448</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45881</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45502</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45628</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44497</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45310</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45361</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45226</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44825</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45888</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44942</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45166</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45579</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45476</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45484</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45152</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44977</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44915</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45910</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45176</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>45149</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45910</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45475</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45517</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>45674</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45911</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45470</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45315</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45590</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45114</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45617</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44979</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45558</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45329</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45917</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45442</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45922</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45103</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45919</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45919</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45919</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45919</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45922</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45919</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45166</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45924</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45924</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45726</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45173</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45726</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45923</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45364</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45470</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44804</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45929</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45454</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44860</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45929</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45929</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45702</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45722</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45932</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45560</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45798</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45677</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45726</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45933</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44732</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45450</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45933</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45937</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45448</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45142</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45805</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45805</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44699</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45805</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44804</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45103</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45939</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44497</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45944</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45944</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44804</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45946</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>44865</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45329</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45950</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45818</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45820</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45825</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45825</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45827</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45954</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45954</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45957</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45020</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44700</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45964</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45612</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45965</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45840</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45841</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45462</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45972</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45974</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45470</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45726</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45972</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45646</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45975</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45726</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45859</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44855</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45726</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45316</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45309</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45225</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45636</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45625</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45975</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45975</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45869</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45875</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45877</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45881</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45982</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45099</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45590</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45244</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45986</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45984</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45986</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45448</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45537</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45191</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>45589</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45988</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45726</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45726</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45616</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45225</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45723</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45996</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45001</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>45478</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45919</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45590</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44861</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46010</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45981</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45993</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45993</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45960</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45593</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45093</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45974</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46029</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46034</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45470</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>46034</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>46034</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45950</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>46034</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>46035</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45538</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45470</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45726</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45152</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45103</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45616</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46045</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46045</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>46050</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44988</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46052</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45786</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46052</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>46056</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>46056</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>46146</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28490,7 +28490,7 @@
         <v>46146</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>46146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>46146</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>46146</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>46148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>46034</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>46147</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46076</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>46072</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>46083</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>46084</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>46084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>46164</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>46169</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46173</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>46173</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46170</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>46170</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>46178</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46181</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46179</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>46179</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>46182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>46183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>46182</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>46188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>46188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>46188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>46188</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>46188</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>46182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>46006</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46197</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>46202</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>46202</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45722</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46205</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46205</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46206</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46206</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>46206</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>46206</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>46211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>46212</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46212</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>46266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46265</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>46265</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46266</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>46266</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46268</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>46268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>46268</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>46268</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>46268</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>46268</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>46273</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>46231</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>46280</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>46239</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>46286</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>46240</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46084</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>46286</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46286</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46286</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>46286</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>46241</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>46241</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46245</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>46288</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46084</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46288</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45722</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45722</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>46286</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45932</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>46247</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>46252</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>46245</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46253</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46252</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46253</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46252</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46252</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46252</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45881</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46076</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>46259</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>46259</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>46262</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>46302</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>46261</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>46302</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>46262</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>46304</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>46304</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46261</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>46304</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>46262</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46304</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>45394</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45404</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45404</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45448</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45412</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45433</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45012</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45219</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45404</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45408</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45447</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45448</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45412</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45785</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45799</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45799</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45799</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45919</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>46146</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>46146</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>46146</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46148</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46149</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46168</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46167</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>46076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44865</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45975</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45975</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46170</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46171</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46179</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45972</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45999</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>46206</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45611</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45946</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45954</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45961</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45994</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46178</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45590</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>46190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>46099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45576</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45617</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46212</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>46273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45105</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>46241</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46247</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46253</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>46302</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45820</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45800</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44690</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44845</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44690</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44487</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44489</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44883</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44792</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44735</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44792</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44812</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44543</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45090</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45442</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45103</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45329</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45589</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45001</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45617</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45099</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45478</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45769</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45309</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45201</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44979</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45303</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45728</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45364</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45475</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44700</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45225</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44825</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45593</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45502</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45470</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45612</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45722</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>44942</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44944</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45888</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45890</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44497</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45616</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45910</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45786</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45919</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>46146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>46147</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45922</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>46146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>46146</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>46146</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45450</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45923</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>46146</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45924</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45924</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45726</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45929</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>46148</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45933</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45933</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45932</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45939</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45084</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45944</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45225</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45944</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45944</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45946</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45950</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45957</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45954</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45954</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45448</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45448</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44860</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45965</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45537</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45818</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45972</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45310</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45975</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45975</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45975</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45975</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45975</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45978</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45590</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>46164</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45982</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45984</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45985</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45986</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45986</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45988</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46169</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45723</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45950</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45996</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45726</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45726</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>46170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>46170</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>46173</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>46173</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45919</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>46010</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45960</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45993</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45993</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45960</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45981</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>46029</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46034</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46179</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>46178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45726</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>46179</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>46045</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>46050</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46182</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>46183</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44819</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45558</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46052</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46052</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>46056</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>46056</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>46182</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45560</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>46034</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>46182</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46188</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46188</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>46188</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46072</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>46076</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45484</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45484</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45476</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>46083</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46084</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45538</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45636</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44915</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45590</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>44988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>46006</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45470</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45517</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>46202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>46202</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45152</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45152</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45450</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45454</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45225</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45722</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>46206</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>46205</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45470</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>46211</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45461</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45593</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46212</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46212</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45628</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45467</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46273</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46273</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45365</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>46231</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44977</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45625</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45020</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45579</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>46281</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45103</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44861</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45616</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>46281</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45364</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>46240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>46239</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>45702</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45726</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46280</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45646</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45722</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>46286</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>46084</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>46286</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45722</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>46084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45448</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>46241</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45244</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>46286</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45176</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>46286</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>46241</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46286</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>46286</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>46245</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46288</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46288</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45590</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45590</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45722</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45932</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45103</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>46247</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45316</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>46245</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>46252</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46252</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45222</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>46252</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45361</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44915</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46252</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45726</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46252</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45881</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>46253</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45470</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45470</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45315</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45114</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45173</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45166</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>46259</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>46259</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>46302</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45726</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45726</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45454</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44804</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>46262</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>46304</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>46301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>46300</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>46045</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46304</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>46301</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45798</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46262</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46304</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45677</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>46262</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>46261</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>46266</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>46266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44732</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45805</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>44699</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>44804</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45805</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>46266</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45805</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45805</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45805</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>46266</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>46261</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46302</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>46268</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>44865</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44497</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45329</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>46268</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>46268</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46268</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>46301</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>46301</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45818</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45820</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46268</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45827</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45840</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45841</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45859</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>44855</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>45869</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45875</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45877</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45394</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45404</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45404</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45448</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>45448</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45412</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45433</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45012</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>45219</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45404</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45408</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45447</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45448</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45013</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45412</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45785</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45799</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45799</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45799</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45919</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>46146</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>46148</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>46148</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>46149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>46148</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>46167</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>46168</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>46168</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>46168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>46175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>46211</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>46076</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44865</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45975</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45975</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45975</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46170</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46171</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>44790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46179</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45972</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45999</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>46206</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45611</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45946</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>45954</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45961</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45994</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46178</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45590</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>46190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>46099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45576</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45617</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46212</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>46273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45105</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>46241</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46247</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46253</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>46302</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45820</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45800</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44690</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44845</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44690</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44487</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44489</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44883</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44792</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44735</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44792</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44812</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44543</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44487</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44741</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45090</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45442</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45103</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45329</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45589</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45001</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45617</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45099</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45478</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45769</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45309</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45201</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44979</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45303</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45728</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45364</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45475</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44700</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45225</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44825</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45593</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45502</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45470</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45612</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45722</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>44942</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44944</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45888</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45890</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44497</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45616</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45910</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45786</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45919</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>46146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>46147</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45922</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>46146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>46146</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>46146</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45450</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45923</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>46146</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45924</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45924</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45726</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45929</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>46148</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45933</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45933</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45932</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45939</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45084</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45944</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45225</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45944</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45944</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45946</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45950</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45957</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45954</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45954</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45448</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45448</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44860</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45965</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45537</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45818</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45972</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45310</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45975</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45975</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45975</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45975</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45975</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45978</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45590</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>46164</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45982</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45984</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45985</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45986</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45986</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45988</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46169</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45723</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45950</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45996</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45726</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45726</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>46170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>46170</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>46173</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>46173</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45919</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>46010</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45960</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45993</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45993</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45960</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45981</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>46029</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46034</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46179</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>46178</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45726</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>46179</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>46045</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>46050</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46182</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>46183</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44819</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45558</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46052</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46052</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>46056</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>46056</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>46182</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45560</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>46034</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>46182</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46188</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46188</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>46188</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46072</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>46076</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45484</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45484</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45476</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>46083</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46084</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45538</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45636</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44915</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45590</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>44988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>46006</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45470</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45517</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>46202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>46202</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45152</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45152</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45450</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45454</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45225</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45722</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>46206</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>46205</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45470</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>46211</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45461</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45593</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46212</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46212</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45628</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45467</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46273</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46273</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45365</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>46231</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44977</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45625</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45020</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45579</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>46281</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45103</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44861</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45616</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>46281</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45364</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>46240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>46239</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>45702</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45726</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46280</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45646</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45722</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>46286</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>46084</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>46286</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45722</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>46084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45448</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>46241</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45244</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>46286</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45176</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>46286</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>46241</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46286</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>46286</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>46245</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46288</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46288</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45590</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45590</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45722</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45932</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45103</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>46247</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45316</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>46245</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>46252</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46252</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45222</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>46252</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45361</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44915</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46252</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>45726</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46252</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45881</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>46253</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45470</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45470</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45315</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45114</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45173</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45166</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>46259</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>46259</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>46302</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45726</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45726</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45454</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44804</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>46262</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>46304</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>46301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>46300</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>46045</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46304</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>46301</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45798</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46262</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46304</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45677</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>46262</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>46261</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>46266</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>46266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44732</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45805</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>44699</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>44804</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45805</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>46266</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45805</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45805</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45805</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>46266</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>46261</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46302</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>46268</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>44865</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44497</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45329</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>46268</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>46268</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46268</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>46301</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>46301</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45818</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45820</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46268</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45827</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45840</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45841</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45859</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>44855</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>45869</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45875</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45877</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45394</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45404</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45404</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45448</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>45448</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45412</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45433</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45012</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>45219</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45404</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45408</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45447</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45448</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45013</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45412</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45785</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45799</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45799</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45799</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45919</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>46146</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>46148</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>46148</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>46149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>46148</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>46167</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>46168</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>46168</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>46168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>46175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>46211</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>44797</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>46315</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45929</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45974</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46170</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>46171</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45975</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>46077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44790</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>46179</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44855</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46206</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>46034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45611</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45726</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44552</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45105</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45946</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46178</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45954</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45961</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46190</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>46212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45994</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45995</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>46241</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45105</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>46247</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45820</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>46099</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>46302</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45576</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>46272</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45617</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45590</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45800</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44690</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>44715</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44845</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44511</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44621</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44624</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44721</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45478</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45890</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45889</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45590</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44861</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44819</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45093</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45910</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46164</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45922</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45919</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45470</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45919</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45919</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45919</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45919</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45919</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45919</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>45924</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45923</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>46169</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45152</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>45929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>46173</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46173</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45929</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45929</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>46170</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45103</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45932</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>46170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45937</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44988</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45939</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45825</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45944</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45944</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45944</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45461</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45946</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45450</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45545</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>46181</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>46179</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>46179</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45454</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>46182</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45593</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45954</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45201</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>46182</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45957</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45303</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45728</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>46188</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>46188</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45964</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45602</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>46188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>46182</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45972</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45974</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45974</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>46197</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45974</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45978</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45975</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45978</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45975</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45975</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45975</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45361</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44825</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>46202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45982</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45984</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46205</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46205</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45985</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>46206</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>46206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>46206</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45988</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>46211</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45723</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46212</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46212</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45996</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45502</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45995</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45950</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45176</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45470</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45315</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45470</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45114</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>46231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45919</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45310</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>46010</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45992</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45981</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45993</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45960</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45960</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45166</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46280</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45726</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45173</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45726</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46281</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46239</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45226</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>46029</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46286</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>46034</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>46240</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46084</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>44804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>46286</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46286</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>45454</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>46034</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46286</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>46035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46286</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46241</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>46241</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45726</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46245</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>46288</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45722</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45722</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45798</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45677</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46045</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46286</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46050</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>44732</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45590</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>46052</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45932</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46247</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>46052</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45805</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45805</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45805</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>44699</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45805</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45805</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44804</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>46056</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>44497</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45222</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>46252</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>44942</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44865</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45329</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>46034</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45818</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45820</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46076</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46245</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>46253</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>46072</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>46252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46253</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45825</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45825</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45827</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46083</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46252</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46252</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46084</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45840</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45881</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46076</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45841</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45579</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45476</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46259</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45859</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44855</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45484</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>46302</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45869</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>46304</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>46261</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>46304</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46304</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45875</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45877</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46301</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46301</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45881</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>44911</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44911</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45538</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>46266</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44915</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45475</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>46045</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45517</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45674</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46262</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46262</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>46300</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46261</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46266</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>46266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46301</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>46301</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>46302</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>46265</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>46266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>46268</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>46268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45950</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46262</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46268</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46268</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45538</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44860</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>46273</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45616</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46273</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46273</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46304</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46315</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46300</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46315</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45560</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45786</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>46146</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46146</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45450</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46146</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46146</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46146</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>46314</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46148</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45448</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45142</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46147</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45103</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45818</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45020</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45612</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45470</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45722</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45726</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45646</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45726</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45726</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45225</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45636</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45625</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45769</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45244</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45726</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45726</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45467</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44904</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44915</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45364</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>44944</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45365</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45448</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45166</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45152</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45149</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>45617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44979</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45558</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45167</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45329</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45442</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45103</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45470</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45702</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45722</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45617</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45726</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44804</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45090</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45594</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44700</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45462</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45316</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45309</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45484</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45099</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45590</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45448</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45225</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45537</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>45191</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45589</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45616</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45225</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45001</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45394</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45404</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45404</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45448</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45448</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45412</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45433</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45012</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45219</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45404</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45408</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45447</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45448</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45013</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45412</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45785</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45799</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45799</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>45799</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45919</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46146</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>46146</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>46146</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46148</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>46148</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>46148</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>46148</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46149</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46168</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>46168</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>46168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46168</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>46167</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>46211</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ARVIDSJAUR.xlsx
+++ b/Översikt ARVIDSJAUR.xlsx
@@ -601,7 +601,7 @@
         <v>45140</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45152</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>45462</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>45469</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45975</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>45964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>44797</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>46315</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45929</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45974</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46170</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>46171</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45975</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>46077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44790</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>46179</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44855</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46206</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>46034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45611</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45726</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44552</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45105</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45946</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46178</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45954</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45961</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46190</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>46212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45994</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45995</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>46241</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45105</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>46247</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45820</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>46099</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>46302</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45576</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>46272</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45617</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45590</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45800</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44690</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>44715</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44845</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44511</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44792</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44792</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44621</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44624</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44792</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44721</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45478</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45890</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45889</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45590</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44861</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44819</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45093</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45910</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46164</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45922</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45919</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45470</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45919</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45919</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45919</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45919</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45919</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45919</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>45924</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45923</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>46169</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45152</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>45929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>46173</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46173</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45929</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45929</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>46170</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45103</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45932</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>46170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45937</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44988</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45939</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45825</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45944</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45944</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45944</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45461</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45946</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45450</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45545</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>46181</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>46179</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>46179</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45454</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>46182</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45593</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45954</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45201</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>46183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>46182</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45957</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45303</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45728</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>46188</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>46188</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45964</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45602</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>46188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>46182</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45972</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45974</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45974</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>46197</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45974</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45978</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45975</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45978</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45628</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45975</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45975</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45975</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45361</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44825</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>46202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45982</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45984</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46205</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46205</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45985</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>46206</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>46206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>46206</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45988</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>46211</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45723</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46212</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46212</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45996</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45502</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45995</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45950</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45176</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45470</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45315</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45470</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45114</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>46231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45919</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45310</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>46010</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45992</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45981</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45993</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45960</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45960</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45166</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46280</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45726</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45173</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45726</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46281</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46239</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45226</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>46029</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46286</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>46034</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>46240</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46084</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>44804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>46286</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>46286</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>45454</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>46034</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>46286</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>46035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46286</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46241</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>46241</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45726</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46245</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>46288</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45722</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45722</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45798</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45677</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46045</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46286</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46050</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>44732</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45590</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>46052</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45932</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46247</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>46052</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45805</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45805</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45805</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>44699</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45805</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45805</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44804</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>46056</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>44497</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45222</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>46252</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>44942</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44865</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45329</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>46034</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45818</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45820</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46076</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46245</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>46253</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>46072</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>46252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46253</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45825</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45825</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45827</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46083</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46252</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46252</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46084</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45840</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45881</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46076</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45841</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45579</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45476</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46259</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45859</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>44855</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45484</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>46302</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45869</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>46304</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>46261</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>46304</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46304</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45875</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45877</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46301</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46301</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45881</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>44911</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44911</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45538</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>46266</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44915</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45475</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>46045</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45517</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45674</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46262</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46262</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>46300</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46261</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46266</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>46266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46301</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>46301</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>46302</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>46265</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>46266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>46268</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>46268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45950</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46262</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46268</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46268</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45538</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44860</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>46273</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45616</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46273</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46273</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46304</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46315</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46300</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46315</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45560</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45786</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>46146</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46146</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45450</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46146</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46146</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46146</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>46314</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46148</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45448</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45142</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46147</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45103</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45818</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45020</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45612</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45470</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45722</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45726</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45646</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45726</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45726</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45225</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45636</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45625</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45769</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45244</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45726</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45726</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45467</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44904</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44915</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45364</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>44944</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45365</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45448</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45166</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45152</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45149</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>45617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44979</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45558</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45167</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45329</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45442</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45103</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45470</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45702</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45722</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45617</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45726</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44804</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45090</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45594</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44700</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45462</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45316</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45309</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45484</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45099</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45590</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45448</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45225</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45537</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>45191</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45589</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45616</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45225</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45001</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45394</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45404</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45404</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45448</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45448</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45412</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45433</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45012</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45219</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45404</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45408</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45447</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45448</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45013</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45412</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45785</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45799</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45799</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>45799</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45919</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46146</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>46146</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>46146</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46148</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>46148</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>46148</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>46148</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46149</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46168</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>46168</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>46168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46168</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>46167</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>46211</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
